--- a/artfynd/A 36211-2026 artfynd.xlsx
+++ b/artfynd/A 36211-2026 artfynd.xlsx
@@ -715,11 +715,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -839,11 +835,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -963,11 +955,7 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 36211-2026 artfynd.xlsx
+++ b/artfynd/A 36211-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137252616</v>
       </c>
       <c r="B2" t="n">
-        <v>57213</v>
+        <v>57223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>137252617</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>57874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>137252619</v>
       </c>
       <c r="B4" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36211-2026 artfynd.xlsx
+++ b/artfynd/A 36211-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137252616</v>
       </c>
       <c r="B2" t="n">
-        <v>57223</v>
+        <v>57224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>137252617</v>
       </c>
       <c r="B3" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>137252619</v>
       </c>
       <c r="B4" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36211-2026 artfynd.xlsx
+++ b/artfynd/A 36211-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>137252617</v>
       </c>
       <c r="B3" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>137252619</v>
       </c>
       <c r="B4" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36211-2026 artfynd.xlsx
+++ b/artfynd/A 36211-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137252616</v>
       </c>
       <c r="B2" t="n">
-        <v>57224</v>
+        <v>57227</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>137252617</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>137252619</v>
       </c>
       <c r="B4" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
